--- a/03_test-cases/v1.0/fragments/TC-TRANGCHU-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-TRANGCHU-v1.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Trang chủ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>

--- a/03_test-cases/v1.0/fragments/TC-TRANGCHU-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-TRANGCHU-v1.0.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$6:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trang chủ'!$A$6:$U$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage Matrix'!$A$1:$M$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G26" s="239" t="inlineStr">
         <is>
-          <t>Tài khoản không có đơn nào ở trạng thái đang hoạt động (Chờ ghép/Đã ghép/Đang giao/Đã giao)</t>
+          <t>Tài khoản không có đơn nào ở trạng thái đang hoạt động (Chờ ghép/Đã ghép/Đang giao/Đã giao/Đã huỷ)</t>
         </is>
       </c>
       <c r="H26" s="239" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="B32" s="239" t="inlineStr">
         <is>
-          <t>REQ-ORD-001</t>
+          <t>REQ-ORD-001, REQ-CNL-001</t>
         </is>
       </c>
       <c r="C32" s="239" t="inlineStr">
         <is>
-          <t>DOC-v1.0-02 §3.1 Table 3</t>
+          <t>Quan sát thực tế app STG (QA GiangDC2, chat 2026-07-30)</t>
         </is>
       </c>
       <c r="D32" s="239" t="inlineStr">
@@ -4938,24 +4938,24 @@
       </c>
       <c r="F32" s="239" t="inlineStr">
         <is>
-          <t>Check thanh progress 5 bước trên card "Đơn của tôi" khớp đúng mốc trạng thái hiện tại</t>
+          <t>Check card "Đơn của tôi" hiển thị badge "Đã huỷ" khi đơn vừa bị huỷ</t>
         </is>
       </c>
       <c r="G32" s="239" t="inlineStr">
         <is>
-          <t>Tài khoản có 1 đơn vai trò Sender ở trạng thái "Đang giao" (mốc thứ 3 trong 5 mốc)</t>
+          <t>Tài khoản có 1 đơn vừa chuyển trạng thái "Đã huỷ" (qua popup "Huỷ đơn")</t>
         </is>
       </c>
       <c r="H32" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco
 2. Bấm tab "Trang chủ" tại bottom nav
-3. Quan sát thanh progress 5 bước trên card trong section "Đơn của tôi"</t>
+3. Quan sát section "Đơn của tôi"</t>
         </is>
       </c>
       <c r="I32" s="239" t="inlineStr">
         <is>
-          <t>3. Thanh progress hiển thị đủ 5 bước và đã đánh dấu đúng tới bước thứ 3 ("Đang giao"); 2 bước còn lại ("Đã giao", "Hoàn thành") chưa được đánh dấu</t>
+          <t>3. Badge trạng thái trên card hiển thị đúng nhãn "Đã huỷ"</t>
         </is>
       </c>
       <c r="J32" s="239" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AP32" s="240" t="inlineStr">
         <is>
-          <t>Technique: EP-in-transit (progress) | Vòng đời chuyển trạng thái test tại module DLV — TC này chỉ verify hiển thị progress theo đúng mốc hiện tại</t>
+          <t>Technique: EP-actor-cancelled-shown | Bổ sung 2026-07-30 theo yêu cầu user, đóng gap phát sinh từ finding tại module Hoạt động: đơn "Đã huỷ" KHÔNG biến mất khỏi các bề mặt hiển thị "đơn hiện tại", card "Đơn của tôi" tại Trang chủ cũng theo đúng rule này.</t>
         </is>
       </c>
     </row>
@@ -5039,29 +5039,29 @@
       </c>
       <c r="E33" s="239" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" s="239" t="inlineStr">
         <is>
-          <t>Check card "Đơn của tôi" hiển thị nhãn hướng "Gửi:" khi user là người gửi của đơn</t>
+          <t>Check thanh progress 5 bước trên card "Đơn của tôi" khớp đúng mốc trạng thái hiện tại</t>
         </is>
       </c>
       <c r="G33" s="239" t="inlineStr">
         <is>
-          <t>Tài khoản là người gửi (Sender) của 1 đơn đang hoạt động</t>
+          <t>Tài khoản có 1 đơn vai trò Sender ở trạng thái "Đang giao" (mốc thứ 3 trong 5 mốc)</t>
         </is>
       </c>
       <c r="H33" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco
 2. Bấm tab "Trang chủ" tại bottom nav
-3. Quan sát nhãn hướng ở đầu card trong section "Đơn của tôi"</t>
+3. Quan sát thanh progress 5 bước trên card trong section "Đơn của tôi"</t>
         </is>
       </c>
       <c r="I33" s="239" t="inlineStr">
         <is>
-          <t>3. Card hiển thị nhãn hướng "Gửi:" kèm loại hàng | giá trị hàng</t>
+          <t>3. Thanh progress hiển thị đủ 5 bước và đã đánh dấu đúng tới bước thứ 3 ("Đang giao"); 2 bước còn lại ("Đã giao", "Hoàn thành") chưa được đánh dấu</t>
         </is>
       </c>
       <c r="J33" s="239" t="inlineStr">
@@ -5106,20 +5106,20 @@
       <c r="AK33" s="240" t="n"/>
       <c r="AL33" s="240" t="n"/>
       <c r="AM33" s="241">
-        <f>IF($A33="","",IF(OR($N33="Yes",$S33="Yes",$X33="Yes",$AC33="Yes",$AH33="Yes"),"Yes","No"))</f>
+        <f>IF($A32="","",IF(OR($N32="Yes",$S32="Yes",$X32="Yes",$AC32="Yes",$AH32="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN33" s="241">
-        <f>IF($A33="","",IFERROR(IF($AI33&lt;&gt;"",$AI33,IF($AD33&lt;&gt;"",$AD33,IF($Y33&lt;&gt;"",$Y33,IF($T33&lt;&gt;"",$T33,IF($O33&lt;&gt;"",$O33,""))))),""))</f>
+        <f>IF($A32="","",IFERROR(IF($AI32&lt;&gt;"",$AI32,IF($AD32&lt;&gt;"",$AD32,IF($Y32&lt;&gt;"",$Y32,IF($T32&lt;&gt;"",$T32,IF($O32&lt;&gt;"",$O32,""))))),""))</f>
         <v/>
       </c>
       <c r="AO33" s="241">
-        <f>IFERROR(IF($AJ33&lt;&gt;"",$AJ33,IF($AE33&lt;&gt;"",$AE33,IF($Z33&lt;&gt;"",$Z33,IF($U33&lt;&gt;"",$U33,IF($P33&lt;&gt;"",$P33,""))))),"")</f>
+        <f>IFERROR(IF($AJ32&lt;&gt;"",$AJ32,IF($AE32&lt;&gt;"",$AE32,IF($Z32&lt;&gt;"",$Z32,IF($U32&lt;&gt;"",$U32,IF($P32&lt;&gt;"",$P32,""))))),"")</f>
         <v/>
       </c>
       <c r="AP33" s="240" t="inlineStr">
         <is>
-          <t>Technique: EP-role-sender</t>
+          <t>Technique: EP-in-transit (progress) | Vòng đời chuyển trạng thái test tại module DLV — TC này chỉ verify hiển thị progress theo đúng mốc hiện tại</t>
         </is>
       </c>
     </row>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="F34" s="239" t="inlineStr">
         <is>
-          <t>Check card "Đơn của tôi" hiển thị nhãn hướng "Nhận:" khi user là người nhận của đơn</t>
+          <t>Check card "Đơn của tôi" hiển thị nhãn hướng "Gửi:" khi user là người gửi của đơn</t>
         </is>
       </c>
       <c r="G34" s="239" t="inlineStr">
         <is>
-          <t>Tài khoản là người nhận (Receiver) của 1 đơn đang hoạt động</t>
+          <t>Tài khoản là người gửi (Sender) của 1 đơn đang hoạt động</t>
         </is>
       </c>
       <c r="H34" s="239" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="I34" s="239" t="inlineStr">
         <is>
-          <t>3. Card hiển thị nhãn hướng "Nhận:" kèm loại hàng | giá trị hàng</t>
+          <t>3. Card hiển thị nhãn hướng "Gửi:" kèm loại hàng | giá trị hàng</t>
         </is>
       </c>
       <c r="J34" s="239" t="inlineStr">
@@ -5212,20 +5212,20 @@
       <c r="AK34" s="240" t="n"/>
       <c r="AL34" s="240" t="n"/>
       <c r="AM34" s="241">
-        <f>IF($A34="","",IF(OR($N34="Yes",$S34="Yes",$X34="Yes",$AC34="Yes",$AH34="Yes"),"Yes","No"))</f>
+        <f>IF($A33="","",IF(OR($N33="Yes",$S33="Yes",$X33="Yes",$AC33="Yes",$AH33="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN34" s="241">
-        <f>IF($A34="","",IFERROR(IF($AI34&lt;&gt;"",$AI34,IF($AD34&lt;&gt;"",$AD34,IF($Y34&lt;&gt;"",$Y34,IF($T34&lt;&gt;"",$T34,IF($O34&lt;&gt;"",$O34,""))))),""))</f>
+        <f>IF($A33="","",IFERROR(IF($AI33&lt;&gt;"",$AI33,IF($AD33&lt;&gt;"",$AD33,IF($Y33&lt;&gt;"",$Y33,IF($T33&lt;&gt;"",$T33,IF($O33&lt;&gt;"",$O33,""))))),""))</f>
         <v/>
       </c>
       <c r="AO34" s="241">
-        <f>IFERROR(IF($AJ34&lt;&gt;"",$AJ34,IF($AE34&lt;&gt;"",$AE34,IF($Z34&lt;&gt;"",$Z34,IF($U34&lt;&gt;"",$U34,IF($P34&lt;&gt;"",$P34,""))))),"")</f>
+        <f>IFERROR(IF($AJ33&lt;&gt;"",$AJ33,IF($AE33&lt;&gt;"",$AE33,IF($Z33&lt;&gt;"",$Z33,IF($U33&lt;&gt;"",$U33,IF($P33&lt;&gt;"",$P33,""))))),"")</f>
         <v/>
       </c>
       <c r="AP34" s="240" t="inlineStr">
         <is>
-          <t>Technique: EP-role-receiver</t>
+          <t>Technique: EP-role-sender</t>
         </is>
       </c>
     </row>
@@ -5246,34 +5246,34 @@
       </c>
       <c r="D35" s="239" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E35" s="239" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F35" s="239" t="inlineStr">
         <is>
-          <t>Check bấm card "Đơn của tôi" điều hướng sang màn Theo dõi đơn đúng đơn đó</t>
+          <t>Check card "Đơn của tôi" hiển thị nhãn hướng "Nhận:" khi user là người nhận của đơn</t>
         </is>
       </c>
       <c r="G35" s="239" t="inlineStr">
         <is>
-          <t>Tài khoản có ít nhất 1 đơn đang hoạt động hiển thị tại section "Đơn của tôi"</t>
+          <t>Tài khoản là người nhận (Receiver) của 1 đơn đang hoạt động</t>
         </is>
       </c>
       <c r="H35" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco
 2. Bấm tab "Trang chủ" tại bottom nav
-3. Bấm vào card trong section "Đơn của tôi" (vùng "Chạm để theo dõi đơn của bạn")</t>
+3. Quan sát nhãn hướng ở đầu card trong section "Đơn của tôi"</t>
         </is>
       </c>
       <c r="I35" s="239" t="inlineStr">
         <is>
-          <t>3. Điều hướng sang màn "Theo dõi đơn" của đúng đơn vừa bấm — loại hàng, tuyến "Từ:"/"Đến:" và trạng thái khớp với nội dung trên card</t>
+          <t>3. Card hiển thị nhãn hướng "Nhận:" kèm loại hàng | giá trị hàng</t>
         </is>
       </c>
       <c r="J35" s="239" t="inlineStr">
@@ -5318,172 +5318,172 @@
       <c r="AK35" s="240" t="n"/>
       <c r="AL35" s="240" t="n"/>
       <c r="AM35" s="241">
+        <f>IF($A34="","",IF(OR($N34="Yes",$S34="Yes",$X34="Yes",$AC34="Yes",$AH34="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN35" s="241">
+        <f>IF($A34="","",IFERROR(IF($AI34&lt;&gt;"",$AI34,IF($AD34&lt;&gt;"",$AD34,IF($Y34&lt;&gt;"",$Y34,IF($T34&lt;&gt;"",$T34,IF($O34&lt;&gt;"",$O34,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO35" s="241">
+        <f>IFERROR(IF($AJ34&lt;&gt;"",$AJ34,IF($AE34&lt;&gt;"",$AE34,IF($Z34&lt;&gt;"",$Z34,IF($U34&lt;&gt;"",$U34,IF($P34&lt;&gt;"",$P34,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP35" s="240" t="inlineStr">
+        <is>
+          <t>Technique: EP-role-receiver</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1" s="206">
+      <c r="A36" s="239">
+        <f>IF(C36="","",$C$2&amp;"."&amp;COUNTA($C$8:C36)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B36" s="239" t="inlineStr">
+        <is>
+          <t>REQ-ORD-001</t>
+        </is>
+      </c>
+      <c r="C36" s="239" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-02 §3.1 Table 3</t>
+        </is>
+      </c>
+      <c r="D36" s="239" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E36" s="239" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" s="239" t="inlineStr">
+        <is>
+          <t>Check bấm card "Đơn của tôi" điều hướng sang màn Theo dõi đơn đúng đơn đó</t>
+        </is>
+      </c>
+      <c r="G36" s="239" t="inlineStr">
+        <is>
+          <t>Tài khoản có ít nhất 1 đơn đang hoạt động hiển thị tại section "Đơn của tôi"</t>
+        </is>
+      </c>
+      <c r="H36" s="239" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco
+2. Bấm tab "Trang chủ" tại bottom nav
+3. Bấm vào card trong section "Đơn của tôi" (vùng "Chạm để theo dõi đơn của bạn")</t>
+        </is>
+      </c>
+      <c r="I36" s="239" t="inlineStr">
+        <is>
+          <t>3. Điều hướng sang màn "Theo dõi đơn" của đúng đơn vừa bấm — loại hàng, tuyến "Từ:"/"Đến:" và trạng thái khớp với nội dung trên card</t>
+        </is>
+      </c>
+      <c r="J36" s="239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K36" s="239" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L36" s="239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M36" s="239" t="n"/>
+      <c r="N36" s="239" t="n"/>
+      <c r="O36" s="239" t="n"/>
+      <c r="P36" s="239" t="n"/>
+      <c r="Q36" s="239" t="n"/>
+      <c r="R36" s="239" t="n"/>
+      <c r="S36" s="239" t="n"/>
+      <c r="T36" s="239" t="n"/>
+      <c r="U36" s="239" t="n"/>
+      <c r="V36" s="239" t="n"/>
+      <c r="W36" s="239" t="n"/>
+      <c r="X36" s="239" t="n"/>
+      <c r="Y36" s="239" t="n"/>
+      <c r="Z36" s="239" t="n"/>
+      <c r="AA36" s="239" t="n"/>
+      <c r="AB36" s="240" t="n"/>
+      <c r="AC36" s="240" t="n"/>
+      <c r="AD36" s="240" t="n"/>
+      <c r="AE36" s="240" t="n"/>
+      <c r="AF36" s="240" t="n"/>
+      <c r="AG36" s="240" t="n"/>
+      <c r="AH36" s="240" t="n"/>
+      <c r="AI36" s="240" t="n"/>
+      <c r="AJ36" s="240" t="n"/>
+      <c r="AK36" s="240" t="n"/>
+      <c r="AL36" s="240" t="n"/>
+      <c r="AM36" s="241">
         <f>IF($A35="","",IF(OR($N35="Yes",$S35="Yes",$X35="Yes",$AC35="Yes",$AH35="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN35" s="241">
+      <c r="AN36" s="241">
         <f>IF($A35="","",IFERROR(IF($AI35&lt;&gt;"",$AI35,IF($AD35&lt;&gt;"",$AD35,IF($Y35&lt;&gt;"",$Y35,IF($T35&lt;&gt;"",$T35,IF($O35&lt;&gt;"",$O35,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO35" s="241">
+      <c r="AO36" s="241">
         <f>IFERROR(IF($AJ35&lt;&gt;"",$AJ35,IF($AE35&lt;&gt;"",$AE35,IF($Z35&lt;&gt;"",$Z35,IF($U35&lt;&gt;"",$U35,IF($P35&lt;&gt;"",$P35,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP35" s="240" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1" s="206">
-      <c r="A36" s="231" t="n"/>
-      <c r="B36" s="232" t="inlineStr">
+      <c r="AP36" s="240" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="206">
+      <c r="A37" s="231" t="n"/>
+      <c r="B37" s="232" t="inlineStr">
         <is>
           <t>Block "Tin mới"</t>
         </is>
       </c>
-      <c r="C36" s="211" t="n"/>
-      <c r="D36" s="211" t="n"/>
-      <c r="E36" s="211" t="n"/>
-      <c r="F36" s="211" t="n"/>
-      <c r="G36" s="211" t="n"/>
-      <c r="H36" s="211" t="n"/>
-      <c r="I36" s="209" t="n"/>
-      <c r="J36" s="231" t="n"/>
-      <c r="K36" s="231" t="n"/>
-      <c r="L36" s="231" t="n"/>
-      <c r="M36" s="231" t="n"/>
-      <c r="N36" s="235" t="n"/>
-      <c r="O36" s="235" t="n"/>
-      <c r="P36" s="235" t="n"/>
-      <c r="Q36" s="235" t="n"/>
-      <c r="R36" s="235" t="n"/>
-      <c r="S36" s="235" t="n"/>
-      <c r="T36" s="235" t="n"/>
-      <c r="U36" s="235" t="n"/>
-      <c r="V36" s="235" t="n"/>
-      <c r="W36" s="235" t="n"/>
-      <c r="X36" s="235" t="n"/>
-      <c r="Y36" s="235" t="n"/>
-      <c r="Z36" s="235" t="n"/>
-      <c r="AA36" s="235" t="n"/>
-      <c r="AB36" s="236" t="n"/>
-      <c r="AC36" s="236" t="n"/>
-      <c r="AD36" s="236" t="n"/>
-      <c r="AE36" s="236" t="n"/>
-      <c r="AF36" s="236" t="n"/>
-      <c r="AG36" s="236" t="n"/>
-      <c r="AH36" s="236" t="n"/>
-      <c r="AI36" s="236" t="n"/>
-      <c r="AJ36" s="236" t="n"/>
-      <c r="AK36" s="236" t="n"/>
-      <c r="AL36" s="236" t="n"/>
-      <c r="AM36" s="237" t="n"/>
-      <c r="AN36" s="237" t="n"/>
-      <c r="AO36" s="237" t="n"/>
-      <c r="AP36" s="238" t="n"/>
-    </row>
-    <row r="37" ht="60" customHeight="1" s="206">
-      <c r="A37" s="239">
-        <f>IF(C37="","",$C$2&amp;"."&amp;COUNTA($C$8:C37)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="239" t="inlineStr">
-        <is>
-          <t>REQ-ASN-005</t>
-        </is>
-      </c>
-      <c r="C37" s="239" t="inlineStr">
-        <is>
-          <t>DOC-v1.0-01 §D7 (OPR-01) + DOC-v1.0-02 §3.1</t>
-        </is>
-      </c>
-      <c r="D37" s="239" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E37" s="239" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F37" s="239" t="inlineStr">
-        <is>
-          <t>Check đầy đủ 2 thành phần tại section "Tin mới" trên Trang chủ</t>
-        </is>
-      </c>
-      <c r="G37" s="239" t="inlineStr">
-        <is>
-          <t>Bảng tin của cộng đồng có ít nhất 1 tin ở trạng thái "Chờ ghép" do người khác đăng</t>
-        </is>
-      </c>
-      <c r="H37" s="239" t="inlineStr">
-        <is>
-          <t>1. Mở app FoxEco
-2. Bấm tab "Trang chủ" tại bottom nav
-3. Quan sát section "Tin mới"</t>
-        </is>
-      </c>
-      <c r="I37" s="239" t="inlineStr">
-        <is>
-          <t>3. Section "Tin mới" hiển thị đủ 2 thành phần: (1) nội dung tin rút gọn của tin mới nhất thuộc CẢ CỘNG ĐỒNG (không giới hạn tin của chính user), (2) vùng bấm để mở màn Chi tiết tin</t>
-        </is>
-      </c>
-      <c r="J37" s="239" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="K37" s="239" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L37" s="239" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M37" s="239" t="n"/>
-      <c r="N37" s="239" t="n"/>
-      <c r="O37" s="239" t="n"/>
-      <c r="P37" s="239" t="n"/>
-      <c r="Q37" s="239" t="n"/>
-      <c r="R37" s="239" t="n"/>
-      <c r="S37" s="239" t="n"/>
-      <c r="T37" s="239" t="n"/>
-      <c r="U37" s="239" t="n"/>
-      <c r="V37" s="239" t="n"/>
-      <c r="W37" s="239" t="n"/>
-      <c r="X37" s="239" t="n"/>
-      <c r="Y37" s="239" t="n"/>
-      <c r="Z37" s="239" t="n"/>
-      <c r="AA37" s="239" t="n"/>
-      <c r="AB37" s="240" t="n"/>
-      <c r="AC37" s="240" t="n"/>
-      <c r="AD37" s="240" t="n"/>
-      <c r="AE37" s="240" t="n"/>
-      <c r="AF37" s="240" t="n"/>
-      <c r="AG37" s="240" t="n"/>
-      <c r="AH37" s="240" t="n"/>
-      <c r="AI37" s="240" t="n"/>
-      <c r="AJ37" s="240" t="n"/>
-      <c r="AK37" s="240" t="n"/>
-      <c r="AL37" s="240" t="n"/>
-      <c r="AM37" s="241">
-        <f>IF($A37="","",IF(OR($N37="Yes",$S37="Yes",$X37="Yes",$AC37="Yes",$AH37="Yes"),"Yes","No"))</f>
-        <v/>
-      </c>
-      <c r="AN37" s="241">
-        <f>IF($A37="","",IFERROR(IF($AI37&lt;&gt;"",$AI37,IF($AD37&lt;&gt;"",$AD37,IF($Y37&lt;&gt;"",$Y37,IF($T37&lt;&gt;"",$T37,IF($O37&lt;&gt;"",$O37,""))))),""))</f>
-        <v/>
-      </c>
-      <c r="AO37" s="241">
-        <f>IFERROR(IF($AJ37&lt;&gt;"",$AJ37,IF($AE37&lt;&gt;"",$AE37,IF($Z37&lt;&gt;"",$Z37,IF($U37&lt;&gt;"",$U37,IF($P37&lt;&gt;"",$P37,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP37" s="240" t="inlineStr">
-        <is>
-          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b) | ⚠ Mâu thuẫn nguồn về SỐ LƯỢNG tin hiển thị: DOC-v1.0-02 §3.1 ghi "rút gọn 1 tin mới nhất" vs DOC-v1.0-01 OPR-01/US-D06 ghi "tối đa 5 tin" — TC này cố ý KHÔNG assert số lượng; cần BA xác nhận (xem 3 TC trần 5 phía dưới)</t>
-        </is>
-      </c>
+      <c r="C37" s="211" t="n"/>
+      <c r="D37" s="211" t="n"/>
+      <c r="E37" s="211" t="n"/>
+      <c r="F37" s="211" t="n"/>
+      <c r="G37" s="211" t="n"/>
+      <c r="H37" s="211" t="n"/>
+      <c r="I37" s="209" t="n"/>
+      <c r="J37" s="231" t="n"/>
+      <c r="K37" s="231" t="n"/>
+      <c r="L37" s="231" t="n"/>
+      <c r="M37" s="231" t="n"/>
+      <c r="N37" s="235" t="n"/>
+      <c r="O37" s="235" t="n"/>
+      <c r="P37" s="235" t="n"/>
+      <c r="Q37" s="235" t="n"/>
+      <c r="R37" s="235" t="n"/>
+      <c r="S37" s="235" t="n"/>
+      <c r="T37" s="235" t="n"/>
+      <c r="U37" s="235" t="n"/>
+      <c r="V37" s="235" t="n"/>
+      <c r="W37" s="235" t="n"/>
+      <c r="X37" s="235" t="n"/>
+      <c r="Y37" s="235" t="n"/>
+      <c r="Z37" s="235" t="n"/>
+      <c r="AA37" s="235" t="n"/>
+      <c r="AB37" s="236" t="n"/>
+      <c r="AC37" s="236" t="n"/>
+      <c r="AD37" s="236" t="n"/>
+      <c r="AE37" s="236" t="n"/>
+      <c r="AF37" s="236" t="n"/>
+      <c r="AG37" s="236" t="n"/>
+      <c r="AH37" s="236" t="n"/>
+      <c r="AI37" s="236" t="n"/>
+      <c r="AJ37" s="236" t="n"/>
+      <c r="AK37" s="236" t="n"/>
+      <c r="AL37" s="236" t="n"/>
+      <c r="AM37" s="237" t="n"/>
+      <c r="AN37" s="237" t="n"/>
+      <c r="AO37" s="237" t="n"/>
+      <c r="AP37" s="238" t="n"/>
     </row>
     <row r="38" ht="60" customHeight="1" s="206">
       <c r="A38" s="239">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="D38" s="239" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E38" s="239" t="inlineStr">
@@ -5512,24 +5512,24 @@
       </c>
       <c r="F38" s="239" t="inlineStr">
         <is>
-          <t>Check bấm 1 tin trong section "Tin mới" điều hướng sang màn Chi tiết tin đúng tin đó</t>
+          <t>Check đầy đủ 2 thành phần tại section "Tin mới" trên Trang chủ</t>
         </is>
       </c>
       <c r="G38" s="239" t="inlineStr">
         <is>
-          <t>Section "Tin mới" đang hiển thị ít nhất 1 tin</t>
+          <t>Bảng tin của cộng đồng có ít nhất 1 tin ở trạng thái "Chờ ghép" do người khác đăng</t>
         </is>
       </c>
       <c r="H38" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco
 2. Bấm tab "Trang chủ" tại bottom nav
-3. Bấm vào 1 tin trong section "Tin mới"</t>
+3. Quan sát section "Tin mới"</t>
         </is>
       </c>
       <c r="I38" s="239" t="inlineStr">
         <is>
-          <t>3. Điều hướng sang màn "Chi tiết tin" của đúng tin vừa bấm — loại hàng, tuyến và khung giờ khớp với nội dung rút gọn hiển thị ở Trang chủ</t>
+          <t>3. Section "Tin mới" hiển thị đủ 2 thành phần: (1) nội dung tin rút gọn của tin mới nhất thuộc CẢ CỘNG ĐỒNG (không giới hạn tin của chính user), (2) vùng bấm để mở màn Chi tiết tin</t>
         </is>
       </c>
       <c r="J38" s="239" t="inlineStr">
@@ -5574,18 +5574,22 @@
       <c r="AK38" s="240" t="n"/>
       <c r="AL38" s="240" t="n"/>
       <c r="AM38" s="241">
-        <f>IF($A38="","",IF(OR($N38="Yes",$S38="Yes",$X38="Yes",$AC38="Yes",$AH38="Yes"),"Yes","No"))</f>
+        <f>IF($A37="","",IF(OR($N37="Yes",$S37="Yes",$X37="Yes",$AC37="Yes",$AH37="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN38" s="241">
-        <f>IF($A38="","",IFERROR(IF($AI38&lt;&gt;"",$AI38,IF($AD38&lt;&gt;"",$AD38,IF($Y38&lt;&gt;"",$Y38,IF($T38&lt;&gt;"",$T38,IF($O38&lt;&gt;"",$O38,""))))),""))</f>
+        <f>IF($A37="","",IFERROR(IF($AI37&lt;&gt;"",$AI37,IF($AD37&lt;&gt;"",$AD37,IF($Y37&lt;&gt;"",$Y37,IF($T37&lt;&gt;"",$T37,IF($O37&lt;&gt;"",$O37,""))))),""))</f>
         <v/>
       </c>
       <c r="AO38" s="241">
-        <f>IFERROR(IF($AJ38&lt;&gt;"",$AJ38,IF($AE38&lt;&gt;"",$AE38,IF($Z38&lt;&gt;"",$Z38,IF($U38&lt;&gt;"",$U38,IF($P38&lt;&gt;"",$P38,""))))),"")</f>
+        <f>IFERROR(IF($AJ37&lt;&gt;"",$AJ37,IF($AE37&lt;&gt;"",$AE37,IF($Z37&lt;&gt;"",$Z37,IF($U37&lt;&gt;"",$U37,IF($P37&lt;&gt;"",$P37,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP38" s="240" t="n"/>
+      <c r="AP38" s="240" t="inlineStr">
+        <is>
+          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b) | ⚠ Mâu thuẫn nguồn về SỐ LƯỢNG tin hiển thị: DOC-v1.0-02 §3.1 ghi "rút gọn 1 tin mới nhất" vs DOC-v1.0-01 OPR-01/US-D06 ghi "tối đa 5 tin" — TC này cố ý KHÔNG assert số lượng; cần BA xác nhận (xem 3 TC trần 5 phía dưới)</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="60" customHeight="1" s="206">
       <c r="A39" s="239">
@@ -5609,29 +5613,29 @@
       </c>
       <c r="E39" s="239" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" s="239" t="inlineStr">
         <is>
-          <t>Check "Tin mới" hiển thị đủ số tin khi số tin phù hợp CHƯA đạt trần 5 (4 tin)</t>
+          <t>Check bấm 1 tin trong section "Tin mới" điều hướng sang màn Chi tiết tin đúng tin đó</t>
         </is>
       </c>
       <c r="G39" s="239" t="inlineStr">
         <is>
-          <t>Carrier đã đăng tuyến OFFER; hệ thống có đúng 4 tin NEED phù hợp tuyến của Carrier</t>
+          <t>Section "Tin mới" đang hiển thị ít nhất 1 tin</t>
         </is>
       </c>
       <c r="H39" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco
 2. Bấm tab "Trang chủ" tại bottom nav
-3. Đếm số tin hiển thị trong section "Tin mới"</t>
+3. Bấm vào 1 tin trong section "Tin mới"</t>
         </is>
       </c>
       <c r="I39" s="239" t="inlineStr">
         <is>
-          <t>3. Section "Tin mới" hiển thị đủ 4 tin, không cắt bớt tin nào</t>
+          <t>3. Điều hướng sang màn "Chi tiết tin" của đúng tin vừa bấm — loại hàng, tuyến và khung giờ khớp với nội dung rút gọn hiển thị ở Trang chủ</t>
         </is>
       </c>
       <c r="J39" s="239" t="inlineStr">
@@ -5676,22 +5680,18 @@
       <c r="AK39" s="240" t="n"/>
       <c r="AL39" s="240" t="n"/>
       <c r="AM39" s="241">
-        <f>IF($A39="","",IF(OR($N39="Yes",$S39="Yes",$X39="Yes",$AC39="Yes",$AH39="Yes"),"Yes","No"))</f>
+        <f>IF($A38="","",IF(OR($N38="Yes",$S38="Yes",$X38="Yes",$AC38="Yes",$AH38="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN39" s="241">
-        <f>IF($A39="","",IFERROR(IF($AI39&lt;&gt;"",$AI39,IF($AD39&lt;&gt;"",$AD39,IF($Y39&lt;&gt;"",$Y39,IF($T39&lt;&gt;"",$T39,IF($O39&lt;&gt;"",$O39,""))))),""))</f>
+        <f>IF($A38="","",IFERROR(IF($AI38&lt;&gt;"",$AI38,IF($AD38&lt;&gt;"",$AD38,IF($Y38&lt;&gt;"",$Y38,IF($T38&lt;&gt;"",$T38,IF($O38&lt;&gt;"",$O38,""))))),""))</f>
         <v/>
       </c>
       <c r="AO39" s="241">
-        <f>IFERROR(IF($AJ39&lt;&gt;"",$AJ39,IF($AE39&lt;&gt;"",$AE39,IF($Z39&lt;&gt;"",$Z39,IF($U39&lt;&gt;"",$U39,IF($P39&lt;&gt;"",$P39,""))))),"")</f>
+        <f>IFERROR(IF($AJ38&lt;&gt;"",$AJ38,IF($AE38&lt;&gt;"",$AE38,IF($Z38&lt;&gt;"",$Z38,IF($U38&lt;&gt;"",$U38,IF($P38&lt;&gt;"",$P38,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP39" s="240" t="inlineStr">
-        <is>
-          <t>Technique: BVA-below-cap (4 tin) | Cần bổ sung test data trong catalog (chưa có bộ tin mẫu theo số lượng khớp tuyến)</t>
-        </is>
-      </c>
+      <c r="AP39" s="240" t="n"/>
     </row>
     <row r="40" ht="60" customHeight="1" s="206">
       <c r="A40" s="239">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="F40" s="239" t="inlineStr">
         <is>
-          <t>Check "Tin mới" hiển thị đúng 5 tin khi số tin phù hợp ĐÚNG BẰNG trần 5</t>
+          <t>Check "Tin mới" hiển thị đủ số tin khi số tin phù hợp CHƯA đạt trần 5 (4 tin)</t>
         </is>
       </c>
       <c r="G40" s="239" t="inlineStr">
         <is>
-          <t>Carrier đã đăng tuyến OFFER; hệ thống có đúng 5 tin NEED phù hợp tuyến của Carrier</t>
+          <t>Carrier đã đăng tuyến OFFER; hệ thống có đúng 4 tin NEED phù hợp tuyến của Carrier</t>
         </is>
       </c>
       <c r="H40" s="239" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="I40" s="239" t="inlineStr">
         <is>
-          <t>3. Section "Tin mới" hiển thị đúng 5 tin</t>
+          <t>3. Section "Tin mới" hiển thị đủ 4 tin, không cắt bớt tin nào</t>
         </is>
       </c>
       <c r="J40" s="239" t="inlineStr">
@@ -5782,20 +5782,20 @@
       <c r="AK40" s="240" t="n"/>
       <c r="AL40" s="240" t="n"/>
       <c r="AM40" s="241">
-        <f>IF($A40="","",IF(OR($N40="Yes",$S40="Yes",$X40="Yes",$AC40="Yes",$AH40="Yes"),"Yes","No"))</f>
+        <f>IF($A39="","",IF(OR($N39="Yes",$S39="Yes",$X39="Yes",$AC39="Yes",$AH39="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN40" s="241">
-        <f>IF($A40="","",IFERROR(IF($AI40&lt;&gt;"",$AI40,IF($AD40&lt;&gt;"",$AD40,IF($Y40&lt;&gt;"",$Y40,IF($T40&lt;&gt;"",$T40,IF($O40&lt;&gt;"",$O40,""))))),""))</f>
+        <f>IF($A39="","",IFERROR(IF($AI39&lt;&gt;"",$AI39,IF($AD39&lt;&gt;"",$AD39,IF($Y39&lt;&gt;"",$Y39,IF($T39&lt;&gt;"",$T39,IF($O39&lt;&gt;"",$O39,""))))),""))</f>
         <v/>
       </c>
       <c r="AO40" s="241">
-        <f>IFERROR(IF($AJ40&lt;&gt;"",$AJ40,IF($AE40&lt;&gt;"",$AE40,IF($Z40&lt;&gt;"",$Z40,IF($U40&lt;&gt;"",$U40,IF($P40&lt;&gt;"",$P40,""))))),"")</f>
+        <f>IFERROR(IF($AJ39&lt;&gt;"",$AJ39,IF($AE39&lt;&gt;"",$AE39,IF($Z39&lt;&gt;"",$Z39,IF($U39&lt;&gt;"",$U39,IF($P39&lt;&gt;"",$P39,""))))),"")</f>
         <v/>
       </c>
       <c r="AP40" s="240" t="inlineStr">
         <is>
-          <t>Technique: BVA-at-cap (5 tin) | Cần bổ sung test data trong catalog</t>
+          <t>Technique: BVA-below-cap (4 tin) | Cần bổ sung test data trong catalog (chưa có bộ tin mẫu theo số lượng khớp tuyến)</t>
         </is>
       </c>
     </row>
@@ -5821,17 +5821,17 @@
       </c>
       <c r="E41" s="239" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F41" s="239" t="inlineStr">
         <is>
-          <t>Check "Tin mới" chỉ hiển thị tối đa 5 tin khi có 6 tin phù hợp</t>
+          <t>Check "Tin mới" hiển thị đúng 5 tin khi số tin phù hợp ĐÚNG BẰNG trần 5</t>
         </is>
       </c>
       <c r="G41" s="239" t="inlineStr">
         <is>
-          <t>Carrier đã đăng tuyến OFFER; hệ thống có 6 tin NEED phù hợp tuyến của Carrier</t>
+          <t>Carrier đã đăng tuyến OFFER; hệ thống có đúng 5 tin NEED phù hợp tuyến của Carrier</t>
         </is>
       </c>
       <c r="H41" s="239" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="I41" s="239" t="inlineStr">
         <is>
-          <t>3. Section "Tin mới" chỉ hiển thị tối đa 5 tin (5 tin mới nhất &amp; gần tuyến nhất); tin thứ 6 KHÔNG hiển thị tại Trang chủ</t>
+          <t>3. Section "Tin mới" hiển thị đúng 5 tin</t>
         </is>
       </c>
       <c r="J41" s="239" t="inlineStr">
@@ -5888,20 +5888,20 @@
       <c r="AK41" s="240" t="n"/>
       <c r="AL41" s="240" t="n"/>
       <c r="AM41" s="241">
-        <f>IF($A41="","",IF(OR($N41="Yes",$S41="Yes",$X41="Yes",$AC41="Yes",$AH41="Yes"),"Yes","No"))</f>
+        <f>IF($A40="","",IF(OR($N40="Yes",$S40="Yes",$X40="Yes",$AC40="Yes",$AH40="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN41" s="241">
-        <f>IF($A41="","",IFERROR(IF($AI41&lt;&gt;"",$AI41,IF($AD41&lt;&gt;"",$AD41,IF($Y41&lt;&gt;"",$Y41,IF($T41&lt;&gt;"",$T41,IF($O41&lt;&gt;"",$O41,""))))),""))</f>
+        <f>IF($A40="","",IFERROR(IF($AI40&lt;&gt;"",$AI40,IF($AD40&lt;&gt;"",$AD40,IF($Y40&lt;&gt;"",$Y40,IF($T40&lt;&gt;"",$T40,IF($O40&lt;&gt;"",$O40,""))))),""))</f>
         <v/>
       </c>
       <c r="AO41" s="241">
-        <f>IFERROR(IF($AJ41&lt;&gt;"",$AJ41,IF($AE41&lt;&gt;"",$AE41,IF($Z41&lt;&gt;"",$Z41,IF($U41&lt;&gt;"",$U41,IF($P41&lt;&gt;"",$P41,""))))),"")</f>
+        <f>IFERROR(IF($AJ40&lt;&gt;"",$AJ40,IF($AE40&lt;&gt;"",$AE40,IF($Z40&lt;&gt;"",$Z40,IF($U40&lt;&gt;"",$U40,IF($P40&lt;&gt;"",$P40,""))))),"")</f>
         <v/>
       </c>
       <c r="AP41" s="240" t="inlineStr">
         <is>
-          <t>Technique: BVA-over-cap (6 tin) | Cần bổ sung test data trong catalog</t>
+          <t>Technique: BVA-at-cap (5 tin) | Cần bổ sung test data trong catalog</t>
         </is>
       </c>
     </row>
@@ -5912,12 +5912,12 @@
       </c>
       <c r="B42" s="239" t="inlineStr">
         <is>
-          <t>REQ-ASN-007</t>
+          <t>REQ-ASN-005</t>
         </is>
       </c>
       <c r="C42" s="239" t="inlineStr">
         <is>
-          <t>DOC-v1.0-01 §D7 (OPR-04)</t>
+          <t>DOC-v1.0-01 §D7 (OPR-01) + DOC-v1.0-02 §3.1</t>
         </is>
       </c>
       <c r="D42" s="239" t="inlineStr">
@@ -5932,24 +5932,24 @@
       </c>
       <c r="F42" s="239" t="inlineStr">
         <is>
-          <t>Check thứ tự tin trong "Tin mới": tin gần tuyến nhất hiển thị trước</t>
+          <t>Check "Tin mới" chỉ hiển thị tối đa 5 tin khi có 6 tin phù hợp</t>
         </is>
       </c>
       <c r="G42" s="239" t="inlineStr">
         <is>
-          <t>Carrier đã đăng tuyến OFFER; có 3 tin NEED phù hợp với độ gần tuyến KHÁC nhau và cùng thời điểm đăng</t>
+          <t>Carrier đã đăng tuyến OFFER; hệ thống có 6 tin NEED phù hợp tuyến của Carrier</t>
         </is>
       </c>
       <c r="H42" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco
 2. Bấm tab "Trang chủ" tại bottom nav
-3. Quan sát thứ tự các tin trong section "Tin mới"</t>
+3. Đếm số tin hiển thị trong section "Tin mới"</t>
         </is>
       </c>
       <c r="I42" s="239" t="inlineStr">
         <is>
-          <t>3. Danh sách sắp xếp theo độ gần tuyến: tin gần tuyến nhất ở vị trí đầu tiên, tin xa tuyến nhất ở cuối</t>
+          <t>3. Section "Tin mới" chỉ hiển thị tối đa 5 tin (5 tin mới nhất &amp; gần tuyến nhất); tin thứ 6 KHÔNG hiển thị tại Trang chủ</t>
         </is>
       </c>
       <c r="J42" s="239" t="inlineStr">
@@ -5994,20 +5994,20 @@
       <c r="AK42" s="240" t="n"/>
       <c r="AL42" s="240" t="n"/>
       <c r="AM42" s="241">
-        <f>IF($A42="","",IF(OR($N42="Yes",$S42="Yes",$X42="Yes",$AC42="Yes",$AH42="Yes"),"Yes","No"))</f>
+        <f>IF($A41="","",IF(OR($N41="Yes",$S41="Yes",$X41="Yes",$AC41="Yes",$AH41="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN42" s="241">
-        <f>IF($A42="","",IFERROR(IF($AI42&lt;&gt;"",$AI42,IF($AD42&lt;&gt;"",$AD42,IF($Y42&lt;&gt;"",$Y42,IF($T42&lt;&gt;"",$T42,IF($O42&lt;&gt;"",$O42,""))))),""))</f>
+        <f>IF($A41="","",IFERROR(IF($AI41&lt;&gt;"",$AI41,IF($AD41&lt;&gt;"",$AD41,IF($Y41&lt;&gt;"",$Y41,IF($T41&lt;&gt;"",$T41,IF($O41&lt;&gt;"",$O41,""))))),""))</f>
         <v/>
       </c>
       <c r="AO42" s="241">
-        <f>IFERROR(IF($AJ42&lt;&gt;"",$AJ42,IF($AE42&lt;&gt;"",$AE42,IF($Z42&lt;&gt;"",$Z42,IF($U42&lt;&gt;"",$U42,IF($P42&lt;&gt;"",$P42,""))))),"")</f>
+        <f>IFERROR(IF($AJ41&lt;&gt;"",$AJ41,IF($AE41&lt;&gt;"",$AE41,IF($Z41&lt;&gt;"",$Z41,IF($U41&lt;&gt;"",$U41,IF($P41&lt;&gt;"",$P41,""))))),"")</f>
         <v/>
       </c>
       <c r="AP42" s="240" t="inlineStr">
         <is>
-          <t>Technique: DT-rule1 (độ gần tuyến khác nhau → sắp theo độ gần) | Cần bổ sung test data trong catalog</t>
+          <t>Technique: BVA-over-cap (6 tin) | Cần bổ sung test data trong catalog</t>
         </is>
       </c>
     </row>
@@ -6038,24 +6038,24 @@
       </c>
       <c r="F43" s="239" t="inlineStr">
         <is>
-          <t>Check thứ tự tin trong "Tin mới" khi độ gần tuyến bằng nhau: tin đăng mới hơn hiển thị trước</t>
+          <t>Check thứ tự tin trong "Tin mới": tin gần tuyến nhất hiển thị trước</t>
         </is>
       </c>
       <c r="G43" s="239" t="inlineStr">
         <is>
-          <t>Carrier đã đăng tuyến OFFER; có 2 tin NEED CÙNG độ gần tuyến nhưng thời điểm đăng khác nhau</t>
+          <t>Carrier đã đăng tuyến OFFER; có 3 tin NEED phù hợp với độ gần tuyến KHÁC nhau và cùng thời điểm đăng</t>
         </is>
       </c>
       <c r="H43" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco
 2. Bấm tab "Trang chủ" tại bottom nav
-3. Quan sát thứ tự 2 tin trong section "Tin mới"</t>
+3. Quan sát thứ tự các tin trong section "Tin mới"</t>
         </is>
       </c>
       <c r="I43" s="239" t="inlineStr">
         <is>
-          <t>3. Tin có thời điểm đăng mới hơn hiển thị trước tin đăng cũ hơn</t>
+          <t>3. Danh sách sắp xếp theo độ gần tuyến: tin gần tuyến nhất ở vị trí đầu tiên, tin xa tuyến nhất ở cuối</t>
         </is>
       </c>
       <c r="J43" s="239" t="inlineStr">
@@ -6100,142 +6100,191 @@
       <c r="AK43" s="240" t="n"/>
       <c r="AL43" s="240" t="n"/>
       <c r="AM43" s="241">
+        <f>IF($A42="","",IF(OR($N42="Yes",$S42="Yes",$X42="Yes",$AC42="Yes",$AH42="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN43" s="241">
+        <f>IF($A42="","",IFERROR(IF($AI42&lt;&gt;"",$AI42,IF($AD42&lt;&gt;"",$AD42,IF($Y42&lt;&gt;"",$Y42,IF($T42&lt;&gt;"",$T42,IF($O42&lt;&gt;"",$O42,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO43" s="241">
+        <f>IFERROR(IF($AJ42&lt;&gt;"",$AJ42,IF($AE42&lt;&gt;"",$AE42,IF($Z42&lt;&gt;"",$Z42,IF($U42&lt;&gt;"",$U42,IF($P42&lt;&gt;"",$P42,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP43" s="240" t="inlineStr">
+        <is>
+          <t>Technique: DT-rule1 (độ gần tuyến khác nhau → sắp theo độ gần) | Cần bổ sung test data trong catalog</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1" s="206">
+      <c r="A44" s="239">
+        <f>IF(C44="","",$C$2&amp;"."&amp;COUNTA($C$8:C44)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B44" s="239" t="inlineStr">
+        <is>
+          <t>REQ-ASN-007</t>
+        </is>
+      </c>
+      <c r="C44" s="239" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D7 (OPR-04)</t>
+        </is>
+      </c>
+      <c r="D44" s="239" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E44" s="239" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F44" s="239" t="inlineStr">
+        <is>
+          <t>Check thứ tự tin trong "Tin mới" khi độ gần tuyến bằng nhau: tin đăng mới hơn hiển thị trước</t>
+        </is>
+      </c>
+      <c r="G44" s="239" t="inlineStr">
+        <is>
+          <t>Carrier đã đăng tuyến OFFER; có 2 tin NEED CÙNG độ gần tuyến nhưng thời điểm đăng khác nhau</t>
+        </is>
+      </c>
+      <c r="H44" s="239" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco
+2. Bấm tab "Trang chủ" tại bottom nav
+3. Quan sát thứ tự 2 tin trong section "Tin mới"</t>
+        </is>
+      </c>
+      <c r="I44" s="239" t="inlineStr">
+        <is>
+          <t>3. Tin có thời điểm đăng mới hơn hiển thị trước tin đăng cũ hơn</t>
+        </is>
+      </c>
+      <c r="J44" s="239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K44" s="239" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L44" s="239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M44" s="239" t="n"/>
+      <c r="N44" s="239" t="n"/>
+      <c r="O44" s="239" t="n"/>
+      <c r="P44" s="239" t="n"/>
+      <c r="Q44" s="239" t="n"/>
+      <c r="R44" s="239" t="n"/>
+      <c r="S44" s="239" t="n"/>
+      <c r="T44" s="239" t="n"/>
+      <c r="U44" s="239" t="n"/>
+      <c r="V44" s="239" t="n"/>
+      <c r="W44" s="239" t="n"/>
+      <c r="X44" s="239" t="n"/>
+      <c r="Y44" s="239" t="n"/>
+      <c r="Z44" s="239" t="n"/>
+      <c r="AA44" s="239" t="n"/>
+      <c r="AB44" s="240" t="n"/>
+      <c r="AC44" s="240" t="n"/>
+      <c r="AD44" s="240" t="n"/>
+      <c r="AE44" s="240" t="n"/>
+      <c r="AF44" s="240" t="n"/>
+      <c r="AG44" s="240" t="n"/>
+      <c r="AH44" s="240" t="n"/>
+      <c r="AI44" s="240" t="n"/>
+      <c r="AJ44" s="240" t="n"/>
+      <c r="AK44" s="240" t="n"/>
+      <c r="AL44" s="240" t="n"/>
+      <c r="AM44" s="241">
         <f>IF($A43="","",IF(OR($N43="Yes",$S43="Yes",$X43="Yes",$AC43="Yes",$AH43="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN43" s="241">
+      <c r="AN44" s="241">
         <f>IF($A43="","",IFERROR(IF($AI43&lt;&gt;"",$AI43,IF($AD43&lt;&gt;"",$AD43,IF($Y43&lt;&gt;"",$Y43,IF($T43&lt;&gt;"",$T43,IF($O43&lt;&gt;"",$O43,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO43" s="241">
+      <c r="AO44" s="241">
         <f>IFERROR(IF($AJ43&lt;&gt;"",$AJ43,IF($AE43&lt;&gt;"",$AE43,IF($Z43&lt;&gt;"",$Z43,IF($U43&lt;&gt;"",$U43,IF($P43&lt;&gt;"",$P43,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP43" s="240" t="inlineStr">
+      <c r="AP44" s="240" t="inlineStr">
         <is>
           <t>Technique: DT-rule2 (độ gần tuyến bằng nhau → sắp theo thời gian đăng mới nhất) | Cần bổ sung test data trong catalog</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1" s="206">
-      <c r="A44" s="231">
-        <f>IF(C44="","",$C$2&amp;"."&amp;COUNTA($C$8:C44)&amp;"")</f>
+    <row r="45" ht="60" customHeight="1" s="206">
+      <c r="A45" s="231">
+        <f>IF(C45="","",$C$2&amp;"."&amp;COUNTA($C$8:C45)&amp;"")</f>
         <v/>
       </c>
-      <c r="B44" s="239" t="inlineStr">
+      <c r="B45" s="239" t="inlineStr">
         <is>
           <t>REQ-ASN-005</t>
         </is>
       </c>
-      <c r="C44" s="239" t="inlineStr">
+      <c r="C45" s="239" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D7 (OPR-01) + DOC-v1.0-02 §3.1</t>
         </is>
       </c>
-      <c r="D44" s="239" t="inlineStr">
+      <c r="D45" s="239" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="E44" s="239" t="inlineStr">
+      <c r="E45" s="239" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F44" s="239" t="inlineStr">
+      <c r="F45" s="239" t="inlineStr">
         <is>
           <t>Check Người gửi cũng thấy section "Tin mới" trên Trang chủ</t>
         </is>
       </c>
-      <c r="G44" s="239" t="inlineStr">
+      <c r="G45" s="239" t="inlineStr">
         <is>
           <t>User đăng nhập với vai trò Sender (CHƯA đăng tuyến OFFER nào); bảng tin cộng đồng có ít nhất 1 tin "Chờ ghép"</t>
         </is>
       </c>
-      <c r="H44" s="239" t="inlineStr">
+      <c r="H45" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Sender
 2. Bấm tab "Trang chủ" tại bottom nav
 3. Cuộn tới vị trí section "Tin mới" và quan sát</t>
         </is>
       </c>
-      <c r="I44" s="239" t="inlineStr">
+      <c r="I45" s="239" t="inlineStr">
         <is>
           <t>3. Section "Tin mới" VẪN hiển thị với vai trò Sender (không phải tính năng riêng của Carrier), nội dung là tin rút gọn của cả cộng đồng</t>
         </is>
       </c>
-      <c r="J44" s="239" t="inlineStr">
+      <c r="J45" s="239" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="K44" s="239" t="inlineStr">
+      <c r="K45" s="239" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="L44" s="239" t="inlineStr">
+      <c r="L45" s="239" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M44" s="231" t="n"/>
-      <c r="N44" s="235" t="n"/>
-      <c r="O44" s="235" t="n"/>
-      <c r="P44" s="235" t="n"/>
-      <c r="Q44" s="235" t="n"/>
-      <c r="R44" s="235" t="n"/>
-      <c r="S44" s="235" t="n"/>
-      <c r="T44" s="235" t="n"/>
-      <c r="U44" s="235" t="n"/>
-      <c r="V44" s="235" t="n"/>
-      <c r="W44" s="235" t="n"/>
-      <c r="X44" s="235" t="n"/>
-      <c r="Y44" s="235" t="n"/>
-      <c r="Z44" s="235" t="n"/>
-      <c r="AA44" s="235" t="n"/>
-      <c r="AB44" s="236" t="n"/>
-      <c r="AC44" s="236" t="n"/>
-      <c r="AD44" s="236" t="n"/>
-      <c r="AE44" s="236" t="n"/>
-      <c r="AF44" s="236" t="n"/>
-      <c r="AG44" s="236" t="n"/>
-      <c r="AH44" s="236" t="n"/>
-      <c r="AI44" s="236" t="n"/>
-      <c r="AJ44" s="236" t="n"/>
-      <c r="AK44" s="236" t="n"/>
-      <c r="AL44" s="236" t="n"/>
-      <c r="AM44" s="237">
-        <f>IF($A44="","",IF(OR($N44="Yes",$S44="Yes",$X44="Yes",$AC44="Yes",$AH44="Yes"),"Yes","No"))</f>
-        <v/>
-      </c>
-      <c r="AN44" s="237">
-        <f>IF($A44="","",IFERROR(IF($AI44&lt;&gt;"",$AI44,IF($AD44&lt;&gt;"",$AD44,IF($Y44&lt;&gt;"",$Y44,IF($T44&lt;&gt;"",$T44,IF($O44&lt;&gt;"",$O44,""))))),""))</f>
-        <v/>
-      </c>
-      <c r="AO44" s="237">
-        <f>IFERROR(IF($AJ44&lt;&gt;"",$AJ44,IF($AE44&lt;&gt;"",$AE44,IF($Z44&lt;&gt;"",$Z44,IF($U44&lt;&gt;"",$U44,IF($P44&lt;&gt;"",$P44,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP44" s="240" t="inlineStr">
-        <is>
-          <t>Technique: EP-role-sender | Nguồn: merge CA v1.1 `C-GENERAL-4` — BRD mô tả "Tin mới" cap-5 là tính năng riêng Carrier nhưng UI cho thấy Trang chủ của Sender cũng có; user chốt "viết theo UI luôn nha" → áp dụng cho CẢ Sender lẫn Carrier. Các TC trần-5/thứ-tự (TC_05.27..31) giữ Given Carrier vì cần tuyến OFFER để xác định độ gần tuyến</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" s="206">
-      <c r="A45" s="231" t="n"/>
-      <c r="B45" s="231" t="n"/>
-      <c r="C45" s="231" t="n"/>
-      <c r="D45" s="231" t="n"/>
-      <c r="E45" s="231" t="n"/>
-      <c r="F45" s="248" t="n"/>
-      <c r="G45" s="248" t="n"/>
-      <c r="H45" s="248" t="n"/>
-      <c r="I45" s="248" t="n"/>
-      <c r="J45" s="231" t="n"/>
-      <c r="K45" s="231" t="n"/>
-      <c r="L45" s="231" t="n"/>
       <c r="M45" s="231" t="n"/>
       <c r="N45" s="235" t="n"/>
       <c r="O45" s="235" t="n"/>
@@ -6262,10 +6311,23 @@
       <c r="AJ45" s="236" t="n"/>
       <c r="AK45" s="236" t="n"/>
       <c r="AL45" s="236" t="n"/>
-      <c r="AM45" s="237" t="n"/>
-      <c r="AN45" s="237" t="n"/>
-      <c r="AO45" s="237" t="n"/>
-      <c r="AP45" s="238" t="n"/>
+      <c r="AM45" s="237">
+        <f>IF($A44="","",IF(OR($N44="Yes",$S44="Yes",$X44="Yes",$AC44="Yes",$AH44="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN45" s="237">
+        <f>IF($A44="","",IFERROR(IF($AI44&lt;&gt;"",$AI44,IF($AD44&lt;&gt;"",$AD44,IF($Y44&lt;&gt;"",$Y44,IF($T44&lt;&gt;"",$T44,IF($O44&lt;&gt;"",$O44,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO45" s="237">
+        <f>IFERROR(IF($AJ44&lt;&gt;"",$AJ44,IF($AE44&lt;&gt;"",$AE44,IF($Z44&lt;&gt;"",$Z44,IF($U44&lt;&gt;"",$U44,IF($P44&lt;&gt;"",$P44,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP45" s="240" t="inlineStr">
+        <is>
+          <t>Technique: EP-role-sender | Nguồn: merge CA v1.1 `C-GENERAL-4` — BRD mô tả "Tin mới" cap-5 là tính năng riêng Carrier nhưng UI cho thấy Trang chủ của Sender cũng có; user chốt "viết theo UI luôn nha" → áp dụng cho CẢ Sender lẫn Carrier. Các TC trần-5/thứ-tự (TC_05.27..31) giữ Given Carrier vì cần tuyến OFFER để xác định độ gần tuyến</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="206">
       <c r="A46" s="231" t="n"/>
@@ -20941,6 +21003,7 @@
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="X5:AB5"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
@@ -20948,7 +21011,6 @@
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="S5:W5"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="B36:I36"/>
   </mergeCells>
   <dataValidations count="8">
     <dataValidation sqref="J8:J17 J19:J502" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
@@ -21203,7 +21265,7 @@
         </is>
       </c>
       <c r="L3" s="252" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M3" s="253" t="inlineStr">
         <is>
@@ -21341,7 +21403,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="205" t="inlineStr">
         <is>
@@ -21352,7 +21413,7 @@
     <row r="8">
       <c r="A8" s="205" t="inlineStr">
         <is>
-          <t>Total TCs derived: 32</t>
+          <t>Total TCs derived: 33</t>
         </is>
       </c>
     </row>
